--- a/Data/EXCEL/Transfer/salemon/202512/7842-salemon-202512.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202512/7842-salemon-202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\202512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202512\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46994FA7-1ECC-4108-A36F-EA1D977A3281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D2EEEE5-6F39-4489-8E8E-F37109307A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="930" windowWidth="26910" windowHeight="18975" xr2:uid="{3B36F661-5571-4AC1-8F9D-46DDB10A96BA}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="17565" windowHeight="11295" xr2:uid="{DCEA074B-1716-4BD2-B7C3-D0F9F16EE723}"/>
   </bookViews>
   <sheets>
     <sheet name="7842-salemon-202512" sheetId="2" r:id="rId1"/>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -857,13 +857,13 @@
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1258,19 +1258,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734E9EB0-0EC3-4320-A601-25D752AADC04}">
-  <dimension ref="A1:Q11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85CE99F-0EF6-4525-8DF2-29C065AC931E}">
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="5" width="12.625" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="13.75" customWidth="1"/>
-    <col min="8" max="9" width="12" customWidth="1"/>
-    <col min="10" max="12" width="12.625" customWidth="1"/>
-    <col min="13" max="14" width="12" customWidth="1"/>
-    <col min="15" max="16" width="12.625" customWidth="1"/>
-    <col min="17" max="17" width="13.125" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
+    <col min="2" max="5" width="7.875" customWidth="1"/>
+    <col min="6" max="6" width="7.5" customWidth="1"/>
+    <col min="7" max="7" width="8.625" customWidth="1"/>
+    <col min="8" max="9" width="7.5" customWidth="1"/>
+    <col min="10" max="12" width="7.875" customWidth="1"/>
+    <col min="13" max="14" width="7.5" customWidth="1"/>
+    <col min="15" max="16" width="7.875" customWidth="1"/>
+    <col min="17" max="17" width="8.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1423,372 +1423,425 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B5" s="6">
-        <v>151.5</v>
+        <v>151</v>
       </c>
       <c r="C5" s="6">
-        <v>151</v>
+        <v>153.5</v>
       </c>
       <c r="D5" s="6">
-        <v>159.5</v>
+        <v>180</v>
       </c>
       <c r="E5" s="6">
-        <v>143.5</v>
+        <v>149</v>
       </c>
       <c r="F5" s="7">
-        <v>-0.5</v>
+        <v>2.5</v>
       </c>
       <c r="G5" s="7">
-        <v>-0.33</v>
+        <v>1.66</v>
       </c>
       <c r="H5" s="8">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="I5" s="7">
-        <v>-9.44</v>
-      </c>
-      <c r="J5" s="9">
-        <v>95.6</v>
+        <v>1.95</v>
+      </c>
+      <c r="I5" s="9">
+        <v>-4.1500000000000004</v>
+      </c>
+      <c r="J5" s="7">
+        <v>122.1</v>
       </c>
       <c r="K5" s="8">
-        <v>20.9</v>
-      </c>
-      <c r="L5" s="9">
-        <v>123.3</v>
+        <v>22.85</v>
+      </c>
+      <c r="L5" s="7">
+        <v>123.2</v>
       </c>
       <c r="M5" s="8">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="N5" s="7">
-        <v>-9.44</v>
-      </c>
-      <c r="O5" s="9">
-        <v>95.6</v>
+        <v>1.95</v>
+      </c>
+      <c r="N5" s="9">
+        <v>-4.1500000000000004</v>
+      </c>
+      <c r="O5" s="7">
+        <v>122.1</v>
       </c>
       <c r="P5" s="8">
-        <v>20.9</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>123.3</v>
+        <v>22.85</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>123.2</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B6" s="12">
-        <v>153.5</v>
+        <v>151.5</v>
       </c>
       <c r="C6" s="12">
-        <v>151.5</v>
+        <v>151</v>
       </c>
       <c r="D6" s="12">
-        <v>157</v>
+        <v>159.5</v>
       </c>
       <c r="E6" s="12">
         <v>143.5</v>
       </c>
       <c r="F6" s="13">
-        <v>-2</v>
+        <v>-0.5</v>
       </c>
       <c r="G6" s="13">
-        <v>-1.3</v>
+        <v>-0.33</v>
       </c>
       <c r="H6" s="14">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="I6" s="15">
-        <v>4.5599999999999996</v>
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="I6" s="13">
+        <v>-9.44</v>
       </c>
       <c r="J6" s="15">
-        <v>128.80000000000001</v>
+        <v>95.6</v>
       </c>
       <c r="K6" s="14">
-        <v>18.87</v>
+        <v>20.9</v>
       </c>
       <c r="L6" s="15">
-        <v>126.8</v>
+        <v>123.3</v>
       </c>
       <c r="M6" s="14">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="N6" s="15">
-        <v>4.5599999999999996</v>
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="N6" s="13">
+        <v>-9.44</v>
       </c>
       <c r="O6" s="15">
-        <v>128.80000000000001</v>
+        <v>95.6</v>
       </c>
       <c r="P6" s="14">
-        <v>18.87</v>
+        <v>20.9</v>
       </c>
       <c r="Q6" s="15">
-        <v>126.8</v>
+        <v>123.3</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B7" s="6">
-        <v>185.5</v>
+        <v>153.5</v>
       </c>
       <c r="C7" s="6">
-        <v>153.5</v>
+        <v>151.5</v>
       </c>
       <c r="D7" s="6">
-        <v>183.5</v>
+        <v>157</v>
       </c>
       <c r="E7" s="6">
-        <v>144</v>
-      </c>
-      <c r="F7" s="7">
-        <v>-32</v>
-      </c>
-      <c r="G7" s="7">
-        <v>-17.25</v>
+        <v>143.5</v>
+      </c>
+      <c r="F7" s="9">
+        <v>-2</v>
+      </c>
+      <c r="G7" s="9">
+        <v>-1.3</v>
       </c>
       <c r="H7" s="8">
-        <v>2.15</v>
-      </c>
-      <c r="I7" s="9">
-        <v>15</v>
-      </c>
-      <c r="J7" s="9">
-        <v>155.4</v>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I7" s="7">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="J7" s="7">
+        <v>128.80000000000001</v>
       </c>
       <c r="K7" s="8">
-        <v>16.63</v>
-      </c>
-      <c r="L7" s="9">
-        <v>126.5</v>
+        <v>18.87</v>
+      </c>
+      <c r="L7" s="7">
+        <v>126.8</v>
       </c>
       <c r="M7" s="8">
-        <v>2.15</v>
-      </c>
-      <c r="N7" s="9">
-        <v>15</v>
-      </c>
-      <c r="O7" s="9">
-        <v>155.4</v>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="N7" s="7">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="O7" s="7">
+        <v>128.80000000000001</v>
       </c>
       <c r="P7" s="8">
-        <v>16.63</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>126.5</v>
+        <v>18.87</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>126.8</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B8" s="12">
-        <v>225</v>
+        <v>185.5</v>
       </c>
       <c r="C8" s="12">
-        <v>185.5</v>
+        <v>153.5</v>
       </c>
       <c r="D8" s="12">
-        <v>225</v>
+        <v>183.5</v>
       </c>
       <c r="E8" s="12">
-        <v>182.5</v>
+        <v>144</v>
       </c>
       <c r="F8" s="13">
-        <v>-39.5</v>
+        <v>-32</v>
       </c>
       <c r="G8" s="13">
-        <v>-17.559999999999999</v>
+        <v>-17.25</v>
       </c>
       <c r="H8" s="14">
-        <v>1.87</v>
-      </c>
-      <c r="I8" s="13">
-        <v>-10.9</v>
+        <v>2.15</v>
+      </c>
+      <c r="I8" s="15">
+        <v>15</v>
       </c>
       <c r="J8" s="15">
-        <v>96.8</v>
+        <v>155.4</v>
       </c>
       <c r="K8" s="14">
-        <v>14.48</v>
+        <v>16.63</v>
       </c>
       <c r="L8" s="15">
-        <v>122.8</v>
+        <v>126.5</v>
       </c>
       <c r="M8" s="14">
-        <v>1.87</v>
-      </c>
-      <c r="N8" s="13">
-        <v>-10.9</v>
+        <v>2.15</v>
+      </c>
+      <c r="N8" s="15">
+        <v>15</v>
       </c>
       <c r="O8" s="15">
-        <v>96.8</v>
+        <v>155.4</v>
       </c>
       <c r="P8" s="14">
-        <v>14.48</v>
+        <v>16.63</v>
       </c>
       <c r="Q8" s="15">
-        <v>122.8</v>
+        <v>126.5</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B9" s="6">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C9" s="6">
+        <v>185.5</v>
+      </c>
+      <c r="D9" s="6">
         <v>225</v>
       </c>
-      <c r="D9" s="6">
-        <v>227</v>
-      </c>
       <c r="E9" s="6">
-        <v>193</v>
+        <v>182.5</v>
       </c>
       <c r="F9" s="9">
-        <v>4</v>
+        <v>-39.5</v>
       </c>
       <c r="G9" s="9">
-        <v>1.81</v>
+        <v>-17.559999999999999</v>
       </c>
       <c r="H9" s="8">
-        <v>2.09</v>
-      </c>
-      <c r="I9" s="7">
-        <v>-15.9</v>
-      </c>
-      <c r="J9" s="9">
-        <v>130.80000000000001</v>
+        <v>1.87</v>
+      </c>
+      <c r="I9" s="9">
+        <v>-10.9</v>
+      </c>
+      <c r="J9" s="7">
+        <v>96.8</v>
       </c>
       <c r="K9" s="8">
-        <v>12.62</v>
-      </c>
-      <c r="L9" s="9">
-        <v>127.2</v>
+        <v>14.48</v>
+      </c>
+      <c r="L9" s="7">
+        <v>122.8</v>
       </c>
       <c r="M9" s="8">
-        <v>2.09</v>
-      </c>
-      <c r="N9" s="7">
-        <v>-15.9</v>
-      </c>
-      <c r="O9" s="9">
-        <v>130.80000000000001</v>
+        <v>1.87</v>
+      </c>
+      <c r="N9" s="9">
+        <v>-10.9</v>
+      </c>
+      <c r="O9" s="7">
+        <v>96.8</v>
       </c>
       <c r="P9" s="8">
-        <v>12.62</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>127.2</v>
+        <v>14.48</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>122.8</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B10" s="12">
-        <v>282.5</v>
+        <v>221</v>
       </c>
       <c r="C10" s="12">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D10" s="12">
-        <v>299</v>
+        <v>227</v>
       </c>
       <c r="E10" s="12">
-        <v>109</v>
-      </c>
-      <c r="F10" s="13">
-        <v>-61.5</v>
-      </c>
-      <c r="G10" s="13">
-        <v>-21.77</v>
+        <v>193</v>
+      </c>
+      <c r="F10" s="15">
+        <v>4</v>
+      </c>
+      <c r="G10" s="15">
+        <v>1.81</v>
       </c>
       <c r="H10" s="14">
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="I10" s="15">
-        <v>5.83</v>
+        <v>2.09</v>
+      </c>
+      <c r="I10" s="13">
+        <v>-15.9</v>
       </c>
       <c r="J10" s="15">
-        <v>174</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="K10" s="14">
-        <v>10.53</v>
+        <v>12.62</v>
       </c>
       <c r="L10" s="15">
-        <v>126.5</v>
+        <v>127.2</v>
       </c>
       <c r="M10" s="14">
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="N10" s="15">
-        <v>5.83</v>
+        <v>2.09</v>
+      </c>
+      <c r="N10" s="13">
+        <v>-15.9</v>
       </c>
       <c r="O10" s="15">
-        <v>174</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="P10" s="14">
-        <v>10.53</v>
+        <v>12.62</v>
       </c>
       <c r="Q10" s="15">
-        <v>126.5</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
+        <v>45809</v>
+      </c>
+      <c r="B11" s="6">
+        <v>282.5</v>
+      </c>
+      <c r="C11" s="6">
+        <v>221</v>
+      </c>
+      <c r="D11" s="6">
+        <v>299</v>
+      </c>
+      <c r="E11" s="6">
+        <v>109</v>
+      </c>
+      <c r="F11" s="9">
+        <v>-61.5</v>
+      </c>
+      <c r="G11" s="9">
+        <v>-21.77</v>
+      </c>
+      <c r="H11" s="8">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="I11" s="7">
+        <v>5.83</v>
+      </c>
+      <c r="J11" s="7">
+        <v>174</v>
+      </c>
+      <c r="K11" s="8">
+        <v>10.53</v>
+      </c>
+      <c r="L11" s="7">
+        <v>126.5</v>
+      </c>
+      <c r="M11" s="8">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="N11" s="7">
+        <v>5.83</v>
+      </c>
+      <c r="O11" s="7">
+        <v>174</v>
+      </c>
+      <c r="P11" s="8">
+        <v>10.53</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>126.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
         <v>45778</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H12" s="14">
         <v>2.35</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J12" s="15">
         <v>218.8</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K12" s="14">
         <v>8.0399999999999991</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L12" s="15">
         <v>115</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M12" s="14">
         <v>2.35</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="N12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O12" s="15">
         <v>218.8</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P12" s="14">
         <v>8.0399999999999991</v>
       </c>
-      <c r="Q11" s="9">
+      <c r="Q12" s="15">
         <v>115</v>
       </c>
     </row>
